--- a/rules/CORE-000616/negative/01/data/unit-test-coreid-FB4403-negative.xlsx
+++ b/rules/CORE-000616/negative/01/data/unit-test-coreid-FB4403-negative.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Source\core-contributor\rules\CORE-000616\negative\01\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04C0158C-42AC-4B1B-9088-011FA5F3751A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C54279FA-F4BE-490D-BF5B-ED2998784C95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Library" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="141">
   <si>
     <t>Product</t>
   </si>
@@ -448,6 +448,18 @@
   </si>
   <si>
     <t>Record</t>
+  </si>
+  <si>
+    <t>[ABSENT]</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Dataset</t>
+  </si>
+  <si>
+    <t>PPSTINT</t>
   </si>
 </sst>
 </file>
@@ -556,7 +568,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -581,7 +593,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -944,7 +955,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1039,6 +1050,86 @@
       </c>
       <c r="E5" t="s">
         <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" t="s">
+        <v>136</v>
+      </c>
+      <c r="D6">
+        <v>6</v>
+      </c>
+      <c r="E6" t="s">
+        <v>140</v>
+      </c>
+      <c r="F6" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" t="s">
+        <v>139</v>
+      </c>
+      <c r="D7" t="s">
+        <v>138</v>
+      </c>
+      <c r="E7" t="s">
+        <v>125</v>
+      </c>
+      <c r="F7" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>4</v>
+      </c>
+      <c r="B8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" t="s">
+        <v>136</v>
+      </c>
+      <c r="D8">
+        <v>8</v>
+      </c>
+      <c r="E8" t="s">
+        <v>140</v>
+      </c>
+      <c r="F8" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>4</v>
+      </c>
+      <c r="B9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>139</v>
+      </c>
+      <c r="D9" t="s">
+        <v>138</v>
+      </c>
+      <c r="E9" t="s">
+        <v>125</v>
+      </c>
+      <c r="F9" t="s">
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -1617,7 +1708,6 @@
       <c r="AE6" t="s">
         <v>103</v>
       </c>
-      <c r="AF6" s="12"/>
     </row>
     <row r="7" spans="1:32" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
@@ -1765,7 +1855,6 @@
       <c r="AE8" t="s">
         <v>103</v>
       </c>
-      <c r="AF8" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1799,11 +1888,11 @@
       <c r="G1" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="H1" s="3" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+      <c r="H1" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>48</v>
       </c>
@@ -1825,8 +1914,8 @@
       <c r="G2" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="H2" s="5" t="s">
-        <v>79</v>
+      <c r="H2" s="7" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -1851,7 +1940,7 @@
       <c r="G3" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="7" t="s">
         <v>80</v>
       </c>
     </row>
@@ -1877,8 +1966,8 @@
       <c r="G4" s="5">
         <v>200</v>
       </c>
-      <c r="H4" s="5">
-        <v>20</v>
+      <c r="H4" s="7" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="30" x14ac:dyDescent="0.25">
@@ -1904,7 +1993,7 @@
         <v>132</v>
       </c>
       <c r="H5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="30" x14ac:dyDescent="0.25">
@@ -1923,8 +2012,8 @@
       <c r="G6" t="s">
         <v>133</v>
       </c>
-      <c r="H6" t="s">
-        <v>104</v>
+      <c r="H6" s="11" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="30" x14ac:dyDescent="0.25">
@@ -1944,7 +2033,7 @@
         <v>134</v>
       </c>
       <c r="H7" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="30" x14ac:dyDescent="0.25">
@@ -1963,8 +2052,8 @@
       <c r="G8" t="s">
         <v>135</v>
       </c>
-      <c r="H8" t="s">
-        <v>104</v>
+      <c r="H8" s="11" t="s">
+        <v>102</v>
       </c>
     </row>
   </sheetData>
